--- a/data/Verzasca/investment_decision/Lavertezzo_district_investment_decision.xlsx
+++ b/data/Verzasca/investment_decision/Lavertezzo_district_investment_decision.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,12 +58,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,24 +461,24 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_all_invested_available_unit</t>
@@ -490,7 +491,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B2" t="n">
@@ -511,13 +512,13 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
+        <v>6.783601386580394</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>2.071637959855438</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>6.783601386580394</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -527,7 +528,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B3" t="n">
@@ -548,13 +549,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>6.783601386580394</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>2.851384043308801</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>6.783601386580394</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -564,7 +565,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B4" t="n">
@@ -585,13 +586,13 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
+        <v>6.783601386580394</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>3.241853795185432</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>6.783601386580394</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -601,7 +602,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B5" t="n">
@@ -622,13 +623,13 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
+        <v>6.783601386580394</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>3.470971714443248</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>6.783601386580394</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -638,7 +639,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B6" t="n">
@@ -659,13 +660,13 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
+        <v>6.783601386580394</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>3.620397691815266</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>6.783601386580394</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -675,11 +676,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1323491215097342</v>
+        <v>0.1276504247294118</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -693,30 +694,30 @@
         <v>6.783601386580394</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1324250513970626</v>
+        <v>0.1176038041411765</v>
       </c>
       <c r="G7" t="n">
+        <v>6.783601386580394</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.1283658579294118</v>
+      </c>
+      <c r="I7" t="n">
         <v>2.071637959855438</v>
       </c>
-      <c r="H7" t="n">
-        <v>0.1323491215097342</v>
-      </c>
-      <c r="I7" t="n">
-        <v>6.783601386580394</v>
-      </c>
       <c r="J7" t="n">
-        <v>0.1323880363055813</v>
+        <v>0.1279169369647059</v>
       </c>
       <c r="K7" t="n">
         <v>2.071637959855438</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1338509005766708</v>
+        <v>0.1610621622352941</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -730,30 +731,30 @@
         <v>6.783601386580394</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1354042943929389</v>
+        <v>0.1610621622352941</v>
       </c>
       <c r="G8" t="n">
+        <v>6.783601386580394</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1703095240941176</v>
+      </c>
+      <c r="I8" t="n">
         <v>2.851384043308801</v>
       </c>
-      <c r="H8" t="n">
-        <v>0.1324499680570641</v>
-      </c>
-      <c r="I8" t="n">
-        <v>6.783601386580394</v>
-      </c>
       <c r="J8" t="n">
-        <v>0.1354042943929389</v>
+        <v>0.1703166510865307</v>
       </c>
       <c r="K8" t="n">
         <v>2.851384043308801</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1363067709084823</v>
+        <v>0.2252205148941177</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -767,30 +768,30 @@
         <v>6.783601386580394</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1365327306747687</v>
+        <v>0.2253537710117647</v>
       </c>
       <c r="G9" t="n">
+        <v>6.783601386580394</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2299408512631796</v>
+      </c>
+      <c r="I9" t="n">
         <v>3.241853795185432</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.1364806481699088</v>
-      </c>
-      <c r="I9" t="n">
-        <v>6.783601386580394</v>
-      </c>
       <c r="J9" t="n">
-        <v>0.1365327306747687</v>
+        <v>0.2263163204153634</v>
       </c>
       <c r="K9" t="n">
         <v>3.241853795185432</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1379557633550962</v>
+        <v>0.2358247362588235</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -804,30 +805,30 @@
         <v>6.783601386580394</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1379758038562418</v>
+        <v>0.2359579923764706</v>
       </c>
       <c r="G10" t="n">
+        <v>6.783601386580394</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.2358247362588236</v>
+      </c>
+      <c r="I10" t="n">
         <v>3.470971714443248</v>
       </c>
-      <c r="H10" t="n">
-        <v>0.1380844722546526</v>
-      </c>
-      <c r="I10" t="n">
-        <v>6.783601386580394</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.1380844722546527</v>
+        <v>0.2362483186913248</v>
       </c>
       <c r="K10" t="n">
         <v>3.470971714443248</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1364539842881596</v>
+        <v>0.2366577375099535</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -841,26 +842,26 @@
         <v>6.783601386580394</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1365327306747687</v>
+        <v>0.2366135934601351</v>
       </c>
       <c r="G11" t="n">
+        <v>6.783601386580394</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.2369367349505811</v>
+      </c>
+      <c r="I11" t="n">
         <v>3.620397691815266</v>
       </c>
-      <c r="H11" t="n">
-        <v>0.1379836257073227</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6.783601386580394</v>
-      </c>
       <c r="J11" t="n">
-        <v>0.1380271645770073</v>
+        <v>0.236703727961913</v>
       </c>
       <c r="K11" t="n">
         <v>3.620397691815266</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B12" t="n">
@@ -897,7 +898,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B13" t="n">
@@ -934,7 +935,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B14" t="n">
@@ -971,7 +972,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B15" t="n">
@@ -1008,7 +1009,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B16" t="n">
@@ -1042,746 +1043,6 @@
       </c>
       <c r="K16" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.005559389441251715</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Lavertezzo</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>175</v>
-      </c>
-      <c r="E17" t="n">
-        <v>4.53915255399319</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.0055628605218153</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4.53915255399319</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.005559389441251713</v>
-      </c>
-      <c r="I17" t="n">
-        <v>4.53915255399319</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.005561168403347583</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4.53915255399319</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.00562804219859739</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Lavertezzo</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>175</v>
-      </c>
-      <c r="E18" t="n">
-        <v>4.53915255399319</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.005699054487341074</v>
-      </c>
-      <c r="G18" t="n">
-        <v>4.53915255399319</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.005563999569129653</v>
-      </c>
-      <c r="I18" t="n">
-        <v>4.53915255399319</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.005699054487341074</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4.53915255399319</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.005740310556623056</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Lavertezzo</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>175</v>
-      </c>
-      <c r="E19" t="n">
-        <v>4.53915255399319</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.005750640145939058</v>
-      </c>
-      <c r="G19" t="n">
-        <v>4.53915255399319</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.005839793665164228</v>
-      </c>
-      <c r="I19" t="n">
-        <v>4.53915255399319</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.005815665461977403</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.53915255399319</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.005906361207834259</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Lavertezzo</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>175</v>
-      </c>
-      <c r="E20" t="n">
-        <v>4.53915255399319</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.006413071300841022</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4.53915255399319</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.00620643826681252</v>
-      </c>
-      <c r="I20" t="n">
-        <v>4.53915255399319</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.006549624418073021</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4.53915255399319</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.005989028800272365</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Lavertezzo</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>175</v>
-      </c>
-      <c r="E21" t="n">
-        <v>4.53915255399319</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.006493055195657947</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4.53915255399319</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.006225063229782896</v>
-      </c>
-      <c r="I21" t="n">
-        <v>4.53915255399319</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.006566259032714961</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.53915255399319</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Lavertezzo</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>8</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.4847437304258241</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.03882163550583918</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.4847437304258241</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.03882163550583918</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Lavertezzo</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.4847437304258241</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.06126234820371228</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.4847437304258241</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.06126234820371228</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Lavertezzo</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>8</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.4847437304258241</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.07625421907189325</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.4847437304258241</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.07625421907189325</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Lavertezzo</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.4847437304258241</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.08728346340446488</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.4847437304258241</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.08728346340446488</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Lavertezzo</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>8</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.4847437304258241</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.09595979696184644</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.4847437304258241</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.09595979696184644</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Lavertezzo</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.934445745399179</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.07483688772209963</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.934445745399179</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.07483688772209963</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Lavertezzo</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.934445745399179</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.1180960929228189</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.934445745399179</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.1180960929228189</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Lavertezzo</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.934445745399179</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.1469960849578665</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.934445745399179</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.1469960849578665</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B30" t="n">
-        <v>0.01913658645792419</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Lavertezzo</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.934445745399179</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.1682572788519805</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.934445745399179</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.1682572788519805</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B31" t="n">
-        <v>0.01913658645792419</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Lavertezzo</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.934445745399179</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.1849827411312703</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.934445745399179</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0.1849827411312703</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Lavertezzo</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>300</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.1292649947802197</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.01035243613489045</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.1292649947802197</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.01035243613489045</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Lavertezzo</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>300</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.1292649947802197</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.01633662618765661</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.1292649947802197</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.01633662618765661</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Lavertezzo</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>300</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.1292649947802197</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.02033445841917154</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.1292649947802197</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.02033445841917154</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B35" t="n">
-        <v>0.1292649947802197</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Lavertezzo</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>300</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.1292649947802197</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.02327559024119064</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.1292649947802197</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.02327559024119064</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B36" t="n">
-        <v>0.1292649947802197</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Lavertezzo</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>300</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.1292649947802197</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.02558927918982572</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.1292649947802197</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.02558927918982572</v>
       </c>
     </row>
   </sheetData>
